--- a/sampleprojects/TaxReturn/excel/states/CO.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/CO.xlsx
@@ -107,7 +107,7 @@
     <t>CO tax = AGI x 4.40%</t>
   </si>
   <si>
-    <t>set result.co_taxable_income = the maximum of result.agi and 0.0; set result.co_tax = result.co_taxable_income * co_tax_rate; add "  CO taxable income: $" + result.co_taxable_income to job.audit_trail; add "  CO state tax (4.40%): $" + result.co_tax to job.audit_trail</t>
+    <t>set result.co_taxable_income = the maximum of result.state_calc_agi and 0.0; set result.co_tax = result.co_taxable_income * co_tax_rate; add "  CO taxable income: $" + result.co_taxable_income to job.audit_trail; add "  CO state tax (4.40%): $" + result.co_tax to job.audit_trail</t>
   </si>
   <si>
     <t>X</t>

--- a/sampleprojects/TaxReturn/excel/states/CO.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/CO.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>DT: co military retirement exemption</t>
   </si>
@@ -38,6 +38,12 @@
     <t>DSL: CONTEXTS</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
     <t>INITIAL ACTIONS: COMMENTS</t>
   </si>
   <si>
@@ -50,16 +56,85 @@
     <t>DSL: CONDITIONS</t>
   </si>
   <si>
-    <t>Age 55 to 64</t>
-  </si>
-  <si>
-    <t>taxpayer.age &gt;= 55 and taxpayer.age &lt;= 64</t>
+    <t>The taxpayer has taxable military retirement benefits (Form 1099-R)</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>54 or younger on December 31 of the tax year</t>
+  </si>
+  <si>
+    <t>job.tax_year - (get yearof taxpayer.date_of_birth) &lt; 55</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t/>
+    <t>65 or older on December 31 of the tax year</t>
+  </si>
+  <si>
+    <t>job.tax_year - (get yearof taxpayer.date_of_birth) &gt;= 65</t>
+  </si>
+  <si>
+    <t>ACTIONS: COMMENTS</t>
+  </si>
+  <si>
+    <t>DSL: ACTIONS</t>
+  </si>
+  <si>
+    <t>DR 0104AD line 7: the lesser of $15,000 and the taxable military retirement benefits (C.R.S. 39-22-104(4)(y))</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and co_military_exemption_under_55 to result.co_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>DR 0104AD line 4, age 55-64: pension and annuity subtraction, the lesser of $20,000 and the pension income (C.R.S. 39-22-104(4)(f))</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and co_pension_subtraction_55_to_64 to result.co_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>DR 0104AD line 4, age 65 and over: the lesser of $24,000 and the pension income</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and co_pension_subtraction_65_plus to result.co_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>Policy:</t>
+  </si>
+  <si>
+    <t>Policy Statements</t>
+  </si>
+  <si>
+    <t>Under 55: military retirement benefits subtraction, DR 0104AD line 7, lesser of $15,000 and the benefits (2025 104 Book p. 19; C.R.S. 39-22-104(4)(y)).</t>
+  </si>
+  <si>
+    <t>55 to 64: a retired servicemember uses the pension and annuity subtraction, DR 0104AD line 4, lesser of $20,000 and the pension (Income Tax Topics: Military Servicemembers, Feb 2025). The $20,000 is shared with other pension income and reduced by Social Security on line 3; only the military pay is counted here.</t>
+  </si>
+  <si>
+    <t>65 and over: pension and annuity subtraction, DR 0104AD line 4, lesser of $24,000 and the pension, with the same sharing caveat.</t>
+  </si>
+  <si>
+    <t>No military retirement benefits for this taxpayer.</t>
+  </si>
+  <si>
+    <t>DT: co pension subtraction</t>
+  </si>
+  <si>
+    <t>COMMENTS: Colorado pension/annuity subtraction (2025). Age-based: 55-64 = $20k, 65+ = $24k. Applies to pension and annuity income not already excluded (e.g., not military retirement which has separate exemption). Source: Colorado DOR Form DR 0104. Skeleton table: condition populated as real EL but actions block intentionally empty pending authorship — subtraction assignment to result.co_pension_subtraction not yet wired up. See issue #446.</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 5791</t>
   </si>
   <si>
     <t>Age 65 or older</t>
@@ -68,21 +143,6 @@
     <t>taxpayer.age &gt;= 65</t>
   </si>
   <si>
-    <t>ACTIONS: COMMENTS</t>
-  </si>
-  <si>
-    <t>DSL: ACTIONS</t>
-  </si>
-  <si>
-    <t>DT: co pension subtraction</t>
-  </si>
-  <si>
-    <t>COMMENTS: Colorado pension/annuity subtraction (2025). Age-based: 55-64 = $20k, 65+ = $24k. Applies to pension and annuity income not already excluded (e.g., not military retirement which has separate exemption). Source: Colorado DOR Form DR 0104. Skeleton table: condition populated as real EL but actions block intentionally empty pending authorship — subtraction assignment to result.co_pension_subtraction not yet wired up. See issue #446.</t>
-  </si>
-  <si>
-    <t>TABLE_NUMBER: 5791</t>
-  </si>
-  <si>
     <t>DT: CO Tax</t>
   </si>
   <si>
@@ -92,7 +152,7 @@
     <t>TABLE_NUMBER: 5792</t>
   </si>
   <si>
-    <t>set result.co_tax = 0; set result.co_taxable_income = 0; add "  Colorado Tax Calculation (Form DR 0104) - flat 4.40%" to job.audit_trail</t>
+    <t>set result.co_tax = 0; set result.co_taxable_income = 0; add "  Colorado Tax Calculation (Form DR 0104) - flat 4.40% of Colorado taxable income" to job.audit_trail; set result.co_military_retirement_exemption = 0.0; perform co_military_retirement_exemption; add "  CO DR 0104AD military retirement / pension subtraction: $" + result.co_military_retirement_exemption to job.audit_trail</t>
   </si>
   <si>
     <t>Always (CO has no filing-status differences)</t>
@@ -101,16 +161,10 @@
     <t>true</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>CO tax = AGI x 4.40%</t>
-  </si>
-  <si>
-    <t>set result.co_taxable_income = the maximum of result.state_calc_agi and 0.0; set result.co_tax = result.co_taxable_income * co_tax_rate; add "  CO taxable income: $" + result.co_taxable_income to job.audit_trail; add "  CO state tax (4.40%): $" + result.co_tax to job.audit_trail</t>
-  </si>
-  <si>
-    <t>X</t>
+    <t>DR 0104 line 1 is federal taxable income (AGI less the federal deductions), line 11 subtracts DR 0104AD (military retirement or pension subtraction), line 13 tax 4.4%</t>
+  </si>
+  <si>
+    <t>set result.co_taxable_income = the maximum of (result.state_calc_agi - (result.state_calc_total_agi - result.taxable_income) - result.co_military_retirement_exemption) and 0.0; set result.co_tax = result.co_taxable_income * co_tax_rate; add "  CO taxable income: $" + result.co_taxable_income to job.audit_trail; add "  CO state tax (4.40%): $" + result.co_tax to job.audit_trail</t>
   </si>
   <si>
     <t>Publish state result to the generic computed_state_tax fields</t>
@@ -119,13 +173,7 @@
     <t>set result.computed_state_taxable_income = result.co_taxable_income; set result.computed_state_tax = result.co_tax</t>
   </si>
   <si>
-    <t>Policy:</t>
-  </si>
-  <si>
-    <t>Policy Statements</t>
-  </si>
-  <si>
-    <t>CO flat tax: 4.40% x AGI per C.R.S. § 39-22-104</t>
+    <t>Colorado flat 4.4% (2025 104 Book) of Colorado taxable income: federal taxable income (DR 0104 line 1, so the federal deduction is already out) less the DR 0104AD subtraction for military retired pay (line 7 under 55; pension and annuity subtraction line 4 at 55 and over). For a non-resident entry the sourced income less the federal deductions stands in for the DR 0104PN apportionment.</t>
   </si>
   <si>
     <t>DT: CO EITC</t>
@@ -209,7 +257,7 @@
     <t>r</t>
   </si>
   <si>
-    <t>CO military retirement exemption for taxpayers age 55-64 (2025). Source: MOAA</t>
+    <t>At 55 and over a retired servicemember uses the pension and annuity subtraction instead (DR 0104AD line 4; C.R.S. 39-22-104(4)(f)): $20,000 at 55-64, less Social Security subtracted on line 3. Same figure as co_pension_subtraction_55_to_64 (Income Tax Topics: Military Servicemembers, Feb 2025).</t>
   </si>
   <si>
     <t>co_military_exemption_65_plus</t>
@@ -218,7 +266,7 @@
     <t>24000.0</t>
   </si>
   <si>
-    <t>CO military retirement exemption for taxpayers age 65+ (2025). Source: MOAA</t>
+    <t>At 65 and over a retired servicemember uses the pension and annuity subtraction (DR 0104AD line 4): $24,000, less Social Security subtracted on line 3. Same figure as co_pension_subtraction_65_plus.</t>
   </si>
   <si>
     <t>co_military_exemption_under_55</t>
@@ -227,13 +275,13 @@
     <t>15000.0</t>
   </si>
   <si>
-    <t>CO military retirement exemption for taxpayers under 55 (2025). Source: MOAA</t>
+    <t>Colorado military retirement benefits subtraction for a taxpayer 54 or younger at year end: the lesser of $15,000 and the taxable military retirement benefits (DR 0104AD line 7; C.R.S. 39-22-104(4)(y); 2025 104 Book p. 19).</t>
   </si>
   <si>
     <t>co_military_retirement_exemption</t>
   </si>
   <si>
-    <t>CO military retirement exemption (computed based on age)</t>
+    <t>Colorado subtraction for military retired pay (computed per taxpayer by co_military_retirement_exemption): under 55 the $15,000 military retirement subtraction (DR 0104AD line 7); 55-64 and 65+ the pension and annuity subtraction, $20,000 and $24,000 (line 4), applied here to the military pay alone (#1330).</t>
   </si>
   <si>
     <t>co_military_retirement_taxable</t>
@@ -843,275 +891,833 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>4</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H11" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1">
-        <v>6</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K11" s="1">
         <v>8</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L11" s="1">
         <v>9</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M11" s="1">
         <v>10</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N11" s="1">
         <v>11</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O11" s="1">
         <v>12</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P11" s="1">
         <v>13</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q11" s="1">
         <v>14</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R11" s="1">
         <v>15</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S11" s="1">
         <v>16</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5">
-        <v>1</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
         <v>2</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>3</v>
+      </c>
+      <c r="G16" s="4">
+        <v>4</v>
+      </c>
+      <c r="H16" s="4">
+        <v>5</v>
+      </c>
+      <c r="I16" s="4">
+        <v>6</v>
+      </c>
+      <c r="J16" s="4">
+        <v>7</v>
+      </c>
+      <c r="K16" s="4">
+        <v>8</v>
+      </c>
+      <c r="L16" s="4">
+        <v>9</v>
+      </c>
+      <c r="M16" s="4">
+        <v>10</v>
+      </c>
+      <c r="N16" s="4">
+        <v>11</v>
+      </c>
+      <c r="O16" s="4">
         <v>12</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="P16" s="4">
         <v>13</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="Q16" s="4">
+        <v>14</v>
+      </c>
+      <c r="R16" s="4">
+        <v>15</v>
+      </c>
+      <c r="S16" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
+        <v>1</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>2</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>3</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="F21" s="1">
+        <v>3</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4</v>
+      </c>
+      <c r="H21" s="1">
+        <v>5</v>
+      </c>
+      <c r="I21" s="1">
+        <v>6</v>
+      </c>
+      <c r="J21" s="1">
+        <v>7</v>
+      </c>
+      <c r="K21" s="1">
+        <v>8</v>
+      </c>
+      <c r="L21" s="1">
+        <v>9</v>
+      </c>
+      <c r="M21" s="1">
+        <v>10</v>
+      </c>
+      <c r="N21" s="1">
+        <v>11</v>
+      </c>
+      <c r="O21" s="1">
+        <v>12</v>
+      </c>
+      <c r="P21" s="1">
         <v>13</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="Q21" s="1">
+        <v>14</v>
+      </c>
+      <c r="R21" s="1">
+        <v>15</v>
+      </c>
+      <c r="S21" s="1">
         <v>16</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="4">
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
         <v>1</v>
       </c>
-      <c r="E14" s="4">
+      <c r="B22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5">
         <v>2</v>
       </c>
-      <c r="F14" s="4">
+      <c r="B23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5">
         <v>3</v>
       </c>
-      <c r="G14" s="4">
+      <c r="B24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5">
         <v>4</v>
       </c>
-      <c r="H14" s="4">
-        <v>5</v>
-      </c>
-      <c r="I14" s="4">
-        <v>6</v>
-      </c>
-      <c r="J14" s="4">
-        <v>7</v>
-      </c>
-      <c r="K14" s="4">
-        <v>8</v>
-      </c>
-      <c r="L14" s="4">
-        <v>9</v>
-      </c>
-      <c r="M14" s="4">
-        <v>10</v>
-      </c>
-      <c r="N14" s="4">
-        <v>11</v>
-      </c>
-      <c r="O14" s="4">
-        <v>12</v>
-      </c>
-      <c r="P14" s="4">
-        <v>13</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>14</v>
-      </c>
-      <c r="R14" s="4">
-        <v>15</v>
-      </c>
-      <c r="S14" s="4">
-        <v>16</v>
+      <c r="B25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:S6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:S8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A21:B21"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1127,7 +1733,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1173,7 +1779,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1196,7 +1802,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1244,11 +1850,11 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1269,11 +1875,11 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -1329,67 +1935,67 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -1467,7 +2073,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1513,7 +2119,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1536,7 +2142,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1584,11 +2190,11 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1612,10 +2218,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -1636,11 +2242,11 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -1696,67 +2302,67 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -1812,58 +2418,58 @@
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -1871,67 +2477,67 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -1987,58 +2593,58 @@
         <v>1</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2070,7 +2676,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2116,7 +2722,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2139,7 +2745,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2187,11 +2793,11 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -2212,11 +2818,11 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -2269,11 +2875,11 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -2360,56 +2966,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -2425,453 +3031,453 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>56</v>
-      </c>
       <c r="D9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>62</v>
-      </c>
       <c r="H12" s="16" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/sampleprojects/TaxReturn/excel/states/CO.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/CO.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>DT: co military retirement exemption</t>
   </si>
@@ -83,6 +83,12 @@
     <t>job.tax_year - (get yearof taxpayer.date_of_birth) &gt;= 65</t>
   </si>
   <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
     <t>ACTIONS: COMMENTS</t>
   </si>
   <si>
@@ -126,6 +132,9 @@
   </si>
   <si>
     <t>No military retirement benefits for this taxpayer.</t>
+  </si>
+  <si>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
   </si>
   <si>
     <t>DT: co pension subtraction</t>
@@ -1023,7 +1032,7 @@
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>6</v>
@@ -1082,7 +1091,7 @@
         <v>18</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>6</v>
@@ -1141,7 +1150,7 @@
         <v>18</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>6</v>
@@ -1177,137 +1186,137 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="s">
+    <row r="15">
+      <c r="A15" s="5">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E17" s="4">
         <v>2</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F17" s="4">
         <v>3</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G17" s="4">
         <v>4</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H17" s="4">
         <v>5</v>
       </c>
-      <c r="I16" s="4">
-        <v>6</v>
-      </c>
-      <c r="J16" s="4">
+      <c r="I17" s="4">
+        <v>6</v>
+      </c>
+      <c r="J17" s="4">
         <v>7</v>
       </c>
-      <c r="K16" s="4">
+      <c r="K17" s="4">
         <v>8</v>
       </c>
-      <c r="L16" s="4">
+      <c r="L17" s="4">
         <v>9</v>
       </c>
-      <c r="M16" s="4">
+      <c r="M17" s="4">
         <v>10</v>
       </c>
-      <c r="N16" s="4">
+      <c r="N17" s="4">
         <v>11</v>
       </c>
-      <c r="O16" s="4">
+      <c r="O17" s="4">
         <v>12</v>
       </c>
-      <c r="P16" s="4">
+      <c r="P17" s="4">
         <v>13</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="Q17" s="4">
         <v>14</v>
       </c>
-      <c r="R16" s="4">
+      <c r="R17" s="4">
         <v>15</v>
       </c>
-      <c r="S16" s="4">
+      <c r="S17" s="4">
         <v>16</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5">
-        <v>1</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>6</v>
@@ -1354,7 +1363,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>28</v>
@@ -1366,10 +1375,10 @@
         <v>6</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>6</v>
@@ -1411,128 +1420,128 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="s">
+    <row r="20">
+      <c r="A20" s="5">
+        <v>3</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1" t="s">
+      <c r="C20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="1">
         <v>1</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E22" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F22" s="1">
         <v>3</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G22" s="1">
         <v>4</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H22" s="1">
         <v>5</v>
       </c>
-      <c r="I21" s="1">
-        <v>6</v>
-      </c>
-      <c r="J21" s="1">
+      <c r="I22" s="1">
+        <v>6</v>
+      </c>
+      <c r="J22" s="1">
         <v>7</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K22" s="1">
         <v>8</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L22" s="1">
         <v>9</v>
       </c>
-      <c r="M21" s="1">
+      <c r="M22" s="1">
         <v>10</v>
       </c>
-      <c r="N21" s="1">
+      <c r="N22" s="1">
         <v>11</v>
       </c>
-      <c r="O21" s="1">
+      <c r="O22" s="1">
         <v>12</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P22" s="1">
         <v>13</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="Q22" s="1">
         <v>14</v>
       </c>
-      <c r="R21" s="1">
+      <c r="R22" s="1">
         <v>15</v>
       </c>
-      <c r="S21" s="1">
+      <c r="S22" s="1">
         <v>16</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5">
-        <v>1</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>6</v>
@@ -1588,10 +1597,10 @@
     </row>
     <row r="24">
       <c r="A24" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>6</v>
@@ -1647,60 +1656,178 @@
     </row>
     <row r="25">
       <c r="A25" s="5">
+        <v>3</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5">
         <v>4</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="S25" s="2" t="s">
+      <c r="B26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5">
+        <v>5</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S27" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1716,8 +1843,8 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:S9"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1733,7 +1860,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1779,7 +1906,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1802,7 +1929,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1935,10 +2062,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
@@ -1991,11 +2118,11 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -2073,7 +2200,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2119,7 +2246,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2142,7 +2269,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2221,7 +2348,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -2302,10 +2429,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -2358,11 +2485,11 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -2418,13 +2545,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -2477,13 +2604,13 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -2533,11 +2660,11 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -2593,7 +2720,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>6</v>
@@ -2676,7 +2803,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2722,7 +2849,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2745,7 +2872,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2875,11 +3002,11 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -2966,56 +3093,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -3034,25 +3161,25 @@
         <v>6</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>6</v>
@@ -3075,25 +3202,25 @@
         <v>6</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>6</v>
@@ -3116,25 +3243,25 @@
         <v>6</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>78</v>
-      </c>
       <c r="H6" s="16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>6</v>
@@ -3157,25 +3284,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>6</v>
@@ -3198,25 +3325,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>6</v>
@@ -3239,25 +3366,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>6</v>
@@ -3280,25 +3407,25 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>6</v>
@@ -3321,25 +3448,25 @@
         <v>6</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>6</v>
@@ -3362,25 +3489,25 @@
         <v>6</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E12" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>78</v>
-      </c>
       <c r="H12" s="16" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>6</v>
@@ -3403,25 +3530,25 @@
         <v>6</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>6</v>
@@ -3444,25 +3571,25 @@
         <v>6</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>6</v>

--- a/sampleprojects/TaxReturn/excel/states/CO.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/CO.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>DT: co military retirement exemption</t>
   </si>
@@ -38,6 +38,12 @@
     <t>DSL: CONTEXTS</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
     <t>INITIAL ACTIONS: COMMENTS</t>
   </si>
   <si>
@@ -50,16 +56,94 @@
     <t>DSL: CONDITIONS</t>
   </si>
   <si>
-    <t>Age 55 to 64</t>
-  </si>
-  <si>
-    <t>taxpayer.age &gt;= 55 and taxpayer.age &lt;= 64</t>
+    <t>The taxpayer has taxable military retirement benefits (Form 1099-R)</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>54 or younger on December 31 of the tax year</t>
+  </si>
+  <si>
+    <t>job.tax_year - (get yearof taxpayer.date_of_birth) &lt; 55</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t/>
+    <t>65 or older on December 31 of the tax year</t>
+  </si>
+  <si>
+    <t>job.tax_year - (get yearof taxpayer.date_of_birth) &gt;= 65</t>
+  </si>
+  <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
+    <t>ACTIONS: COMMENTS</t>
+  </si>
+  <si>
+    <t>DSL: ACTIONS</t>
+  </si>
+  <si>
+    <t>DR 0104AD line 7: the lesser of $15,000 and the taxable military retirement benefits (C.R.S. 39-22-104(4)(y))</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and co_military_exemption_under_55 to result.co_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>DR 0104AD line 4, age 55-64: pension and annuity subtraction, the lesser of $20,000 and the pension income (C.R.S. 39-22-104(4)(f))</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and co_pension_subtraction_55_to_64 to result.co_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>DR 0104AD line 4, age 65 and over: the lesser of $24,000 and the pension income</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and co_pension_subtraction_65_plus to result.co_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>Policy:</t>
+  </si>
+  <si>
+    <t>Policy Statements</t>
+  </si>
+  <si>
+    <t>Under 55: military retirement benefits subtraction, DR 0104AD line 7, lesser of $15,000 and the benefits (2025 104 Book p. 19; C.R.S. 39-22-104(4)(y)).</t>
+  </si>
+  <si>
+    <t>55 to 64: a retired servicemember uses the pension and annuity subtraction, DR 0104AD line 4, lesser of $20,000 and the pension (Income Tax Topics: Military Servicemembers, Feb 2025). The $20,000 is shared with other pension income and reduced by Social Security on line 3; only the military pay is counted here.</t>
+  </si>
+  <si>
+    <t>65 and over: pension and annuity subtraction, DR 0104AD line 4, lesser of $24,000 and the pension, with the same sharing caveat.</t>
+  </si>
+  <si>
+    <t>No military retirement benefits for this taxpayer.</t>
+  </si>
+  <si>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
+  </si>
+  <si>
+    <t>DT: co pension subtraction</t>
+  </si>
+  <si>
+    <t>COMMENTS: Colorado pension/annuity subtraction (2025). Age-based: 55-64 = $20k, 65+ = $24k. Applies to pension and annuity income not already excluded (e.g., not military retirement which has separate exemption). Source: Colorado DOR Form DR 0104. Skeleton table: condition populated as real EL but actions block intentionally empty pending authorship — subtraction assignment to result.co_pension_subtraction not yet wired up. See issue #446.</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 5791</t>
   </si>
   <si>
     <t>Age 65 or older</t>
@@ -68,21 +152,6 @@
     <t>taxpayer.age &gt;= 65</t>
   </si>
   <si>
-    <t>ACTIONS: COMMENTS</t>
-  </si>
-  <si>
-    <t>DSL: ACTIONS</t>
-  </si>
-  <si>
-    <t>DT: co pension subtraction</t>
-  </si>
-  <si>
-    <t>COMMENTS: Colorado pension/annuity subtraction (2025). Age-based: 55-64 = $20k, 65+ = $24k. Applies to pension and annuity income not already excluded (e.g., not military retirement which has separate exemption). Source: Colorado DOR Form DR 0104. Skeleton table: condition populated as real EL but actions block intentionally empty pending authorship — subtraction assignment to result.co_pension_subtraction not yet wired up. See issue #446.</t>
-  </si>
-  <si>
-    <t>TABLE_NUMBER: 5791</t>
-  </si>
-  <si>
     <t>DT: CO Tax</t>
   </si>
   <si>
@@ -92,7 +161,7 @@
     <t>TABLE_NUMBER: 5792</t>
   </si>
   <si>
-    <t>set result.co_tax = 0; set result.co_taxable_income = 0; add "  Colorado Tax Calculation (Form DR 0104) - flat 4.40%" to job.audit_trail</t>
+    <t>set result.co_tax = 0; set result.co_taxable_income = 0; add "  Colorado Tax Calculation (Form DR 0104) - flat 4.40% of Colorado taxable income" to job.audit_trail; set result.co_military_retirement_exemption = 0.0; perform co_military_retirement_exemption; add "  CO DR 0104AD military retirement / pension subtraction: $" + result.co_military_retirement_exemption to job.audit_trail</t>
   </si>
   <si>
     <t>Always (CO has no filing-status differences)</t>
@@ -101,16 +170,10 @@
     <t>true</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>CO tax = AGI x 4.40%</t>
-  </si>
-  <si>
-    <t>set result.co_taxable_income = the maximum of result.state_calc_agi and 0.0; set result.co_tax = result.co_taxable_income * co_tax_rate; add "  CO taxable income: $" + result.co_taxable_income to job.audit_trail; add "  CO state tax (4.40%): $" + result.co_tax to job.audit_trail</t>
-  </si>
-  <si>
-    <t>X</t>
+    <t>DR 0104 line 1 is federal taxable income (AGI less the federal deductions), line 11 subtracts DR 0104AD (military retirement or pension subtraction), line 13 tax 4.4%</t>
+  </si>
+  <si>
+    <t>set result.co_taxable_income = the maximum of (result.state_calc_agi - (result.state_calc_total_agi - result.taxable_income) - result.co_military_retirement_exemption) and 0.0; set result.co_tax = result.co_taxable_income * co_tax_rate; add "  CO taxable income: $" + result.co_taxable_income to job.audit_trail; add "  CO state tax (4.40%): $" + result.co_tax to job.audit_trail</t>
   </si>
   <si>
     <t>Publish state result to the generic computed_state_tax fields</t>
@@ -119,13 +182,7 @@
     <t>set result.computed_state_taxable_income = result.co_taxable_income; set result.computed_state_tax = result.co_tax</t>
   </si>
   <si>
-    <t>Policy:</t>
-  </si>
-  <si>
-    <t>Policy Statements</t>
-  </si>
-  <si>
-    <t>CO flat tax: 4.40% x AGI per C.R.S. § 39-22-104</t>
+    <t>Colorado flat 4.4% (2025 104 Book) of Colorado taxable income: federal taxable income (DR 0104 line 1, so the federal deduction is already out) less the DR 0104AD subtraction for military retired pay (line 7 under 55; pension and annuity subtraction line 4 at 55 and over). For a non-resident entry the sourced income less the federal deductions stands in for the DR 0104PN apportionment.</t>
   </si>
   <si>
     <t>DT: CO EITC</t>
@@ -209,7 +266,7 @@
     <t>r</t>
   </si>
   <si>
-    <t>CO military retirement exemption for taxpayers age 55-64 (2025). Source: MOAA</t>
+    <t>At 55 and over a retired servicemember uses the pension and annuity subtraction instead (DR 0104AD line 4; C.R.S. 39-22-104(4)(f)): $20,000 at 55-64, less Social Security subtracted on line 3. Same figure as co_pension_subtraction_55_to_64 (Income Tax Topics: Military Servicemembers, Feb 2025).</t>
   </si>
   <si>
     <t>co_military_exemption_65_plus</t>
@@ -218,7 +275,7 @@
     <t>24000.0</t>
   </si>
   <si>
-    <t>CO military retirement exemption for taxpayers age 65+ (2025). Source: MOAA</t>
+    <t>At 65 and over a retired servicemember uses the pension and annuity subtraction (DR 0104AD line 4): $24,000, less Social Security subtracted on line 3. Same figure as co_pension_subtraction_65_plus.</t>
   </si>
   <si>
     <t>co_military_exemption_under_55</t>
@@ -227,13 +284,13 @@
     <t>15000.0</t>
   </si>
   <si>
-    <t>CO military retirement exemption for taxpayers under 55 (2025). Source: MOAA</t>
+    <t>Colorado military retirement benefits subtraction for a taxpayer 54 or younger at year end: the lesser of $15,000 and the taxable military retirement benefits (DR 0104AD line 7; C.R.S. 39-22-104(4)(y); 2025 104 Book p. 19).</t>
   </si>
   <si>
     <t>co_military_retirement_exemption</t>
   </si>
   <si>
-    <t>CO military retirement exemption (computed based on age)</t>
+    <t>Colorado subtraction for military retired pay (computed per taxpayer by co_military_retirement_exemption): under 55 the $15,000 military retirement subtraction (DR 0104AD line 7); 55-64 and 65+ the pension and annuity subtraction, $20,000 and $24,000 (line 4), applied here to the military pay alone (#1330).</t>
   </si>
   <si>
     <t>co_military_retirement_taxable</t>
@@ -843,275 +900,951 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>4</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H11" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1">
-        <v>6</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K11" s="1">
         <v>8</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L11" s="1">
         <v>9</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M11" s="1">
         <v>10</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N11" s="1">
         <v>11</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O11" s="1">
         <v>12</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P11" s="1">
         <v>13</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q11" s="1">
         <v>14</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R11" s="1">
         <v>15</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S11" s="1">
         <v>16</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5">
-        <v>1</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
         <v>2</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4">
+        <v>3</v>
+      </c>
+      <c r="G17" s="4">
+        <v>4</v>
+      </c>
+      <c r="H17" s="4">
+        <v>5</v>
+      </c>
+      <c r="I17" s="4">
+        <v>6</v>
+      </c>
+      <c r="J17" s="4">
+        <v>7</v>
+      </c>
+      <c r="K17" s="4">
+        <v>8</v>
+      </c>
+      <c r="L17" s="4">
+        <v>9</v>
+      </c>
+      <c r="M17" s="4">
+        <v>10</v>
+      </c>
+      <c r="N17" s="4">
+        <v>11</v>
+      </c>
+      <c r="O17" s="4">
         <v>12</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="P17" s="4">
         <v>13</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="Q17" s="4">
+        <v>14</v>
+      </c>
+      <c r="R17" s="4">
+        <v>15</v>
+      </c>
+      <c r="S17" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>3</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="F22" s="1">
+        <v>3</v>
+      </c>
+      <c r="G22" s="1">
+        <v>4</v>
+      </c>
+      <c r="H22" s="1">
+        <v>5</v>
+      </c>
+      <c r="I22" s="1">
+        <v>6</v>
+      </c>
+      <c r="J22" s="1">
+        <v>7</v>
+      </c>
+      <c r="K22" s="1">
+        <v>8</v>
+      </c>
+      <c r="L22" s="1">
+        <v>9</v>
+      </c>
+      <c r="M22" s="1">
+        <v>10</v>
+      </c>
+      <c r="N22" s="1">
+        <v>11</v>
+      </c>
+      <c r="O22" s="1">
+        <v>12</v>
+      </c>
+      <c r="P22" s="1">
         <v>13</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="Q22" s="1">
+        <v>14</v>
+      </c>
+      <c r="R22" s="1">
+        <v>15</v>
+      </c>
+      <c r="S22" s="1">
         <v>16</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="4">
+    </row>
+    <row r="23">
+      <c r="A23" s="5">
         <v>1</v>
       </c>
-      <c r="E14" s="4">
+      <c r="B23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5">
         <v>2</v>
       </c>
-      <c r="F14" s="4">
+      <c r="B24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5">
         <v>3</v>
       </c>
-      <c r="G14" s="4">
+      <c r="B25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5">
         <v>4</v>
       </c>
-      <c r="H14" s="4">
+      <c r="B26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5">
         <v>5</v>
       </c>
-      <c r="I14" s="4">
-        <v>6</v>
-      </c>
-      <c r="J14" s="4">
-        <v>7</v>
-      </c>
-      <c r="K14" s="4">
-        <v>8</v>
-      </c>
-      <c r="L14" s="4">
-        <v>9</v>
-      </c>
-      <c r="M14" s="4">
-        <v>10</v>
-      </c>
-      <c r="N14" s="4">
-        <v>11</v>
-      </c>
-      <c r="O14" s="4">
-        <v>12</v>
-      </c>
-      <c r="P14" s="4">
-        <v>13</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>14</v>
-      </c>
-      <c r="R14" s="4">
-        <v>15</v>
-      </c>
-      <c r="S14" s="4">
-        <v>16</v>
+      <c r="B27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:S6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:S8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1127,7 +1860,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1173,7 +1906,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1196,7 +1929,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1244,11 +1977,11 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1269,11 +2002,11 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -1329,67 +2062,67 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -1467,7 +2200,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1513,7 +2246,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1536,7 +2269,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1584,11 +2317,11 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1612,10 +2345,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -1636,11 +2369,11 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -1696,67 +2429,67 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -1812,58 +2545,58 @@
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -1871,67 +2604,67 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -1987,58 +2720,58 @@
         <v>1</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2070,7 +2803,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2116,7 +2849,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2139,7 +2872,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2187,11 +2920,11 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -2212,11 +2945,11 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -2269,11 +3002,11 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -2360,56 +3093,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -2425,453 +3158,453 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E13" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>62</v>
-      </c>
       <c r="H13" s="16" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
